--- a/survey_templates/044_ethical_use_of_ai_in_learning_survey--survey_templates.xlsx
+++ b/survey_templates/044_ethical_use_of_ai_in_learning_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1167,8 +1167,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1196,12 +1196,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'ai-expert'}</t>
+          <t>ai-expert</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'AI-Expert'}</t>
+          <t>AI-Expert</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'ai-novice'}</t>
+          <t>ai-novice</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'AI-Novice'}</t>
+          <t>AI-Novice</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'improved_student_outcomes'}</t>
+          <t>improved_student_outcomes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Improved student outcomes'}</t>
+          <t>Improved student outcomes</t>
         </is>
       </c>
     </row>
@@ -1264,12 +1264,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'increased_teacher_efficiency'}</t>
+          <t>increased_teacher_efficiency</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Increased teacher efficiency'}</t>
+          <t>Increased teacher efficiency</t>
         </is>
       </c>
     </row>
@@ -1281,12 +1281,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'privacy'}</t>
+          <t>privacy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Privacy'}</t>
+          <t>Privacy</t>
         </is>
       </c>
     </row>
@@ -1315,12 +1315,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'security'}</t>
+          <t>security</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Security'}</t>
+          <t>Security</t>
         </is>
       </c>
     </row>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'cost'}</t>
+          <t>cost</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Cost'}</t>
+          <t>Cost</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1366,12 +1366,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'transparency'}</t>
+          <t>transparency</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Transparency'}</t>
+          <t>Transparency</t>
         </is>
       </c>
     </row>
@@ -1383,12 +1383,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'accountability'}</t>
+          <t>accountability</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Accountability'}</t>
+          <t>Accountability</t>
         </is>
       </c>
     </row>
@@ -1400,12 +1400,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'ai-expert'}</t>
+          <t>ai-expert</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'AI-Expert'}</t>
+          <t>AI-Expert</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'ai-novice'}</t>
+          <t>ai-novice</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'AI-Novice'}</t>
+          <t>AI-Novice</t>
         </is>
       </c>
     </row>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1468,12 +1468,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'small'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Small'}</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
@@ -1485,12 +1485,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1502,12 +1502,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'large'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Large'}</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
@@ -1519,12 +1519,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1536,12 +1536,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'elementary_school'}</t>
+          <t>elementary_school</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Elementary School'}</t>
+          <t>Elementary School</t>
         </is>
       </c>
     </row>
@@ -1553,12 +1553,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'High School'}</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'college'}</t>
+          <t>college</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'College'}</t>
+          <t>College</t>
         </is>
       </c>
     </row>
@@ -1587,12 +1587,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1604,12 +1604,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'0-5'}</t>
+          <t>0-5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': '0-5'}</t>
+          <t>0-5</t>
         </is>
       </c>
     </row>
@@ -1621,12 +1621,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'6-15'}</t>
+          <t>6-15</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': '6-15'}</t>
+          <t>6-15</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'16-25'}</t>
+          <t>16-25</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': '16-25'}</t>
+          <t>16-25</t>
         </is>
       </c>
     </row>
@@ -1655,12 +1655,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'26+'}</t>
+          <t>26+</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': '26+'}</t>
+          <t>26+</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'it'}</t>
+          <t>it</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'IT'}</t>
+          <t>IT</t>
         </is>
       </c>
     </row>
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'curriculum_development'}</t>
+          <t>curriculum_development</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Curriculum Development'}</t>
+          <t>Curriculum Development</t>
         </is>
       </c>
     </row>
@@ -1706,12 +1706,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1723,12 +1723,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1740,12 +1740,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
